--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62596.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62596.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>KG.1103</t>
+          <t>IG.1103</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jp</t>
+          <t>Xdl</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ALYLAL</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G74H</t>
+          <t>G98D</t>
         </is>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62596.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62596.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>17/11/2025</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G98D</t>
+          <t>G88C</t>
         </is>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62596.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62596.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Xdl</t>
+          <t>Erl</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>R</t>
         </is>
       </c>
     </row>
@@ -700,10 +700,10 @@
         <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>6241</v>
+        <v>1103</v>
       </c>
       <c r="K4" t="n">
-        <v>1011</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +724,7 @@
         <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>2.1</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62596.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62596.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Erl</t>
+          <t>ERL</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
         <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>1103</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
         <v>1021</v>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62596.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62596.xlsx
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -703,7 +703,7 @@
         <v>1.03</v>
       </c>
       <c r="K4" t="n">
-        <v>1021</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5">
